--- a/data/trans_dic/BARTHEL_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/BARTHEL_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,79; 97,47</t>
+          <t>2,56; 23,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,68; 93,27</t>
+          <t>6,68; 29,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,82; 85,5</t>
+          <t>14,56; 41,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86,14; 98,4</t>
+          <t>2,46; 15,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,75; 100,0</t>
+          <t>0,0; 23,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,2; 68,99</t>
+          <t>30,78; 60,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,83; 77,12</t>
+          <t>22,97; 53,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78,45; 92,07</t>
+          <t>7,35; 21,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83,96; 97,27</t>
+          <t>3,44; 15,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,49; 77,96</t>
+          <t>21,54; 40,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,39; 77,98</t>
+          <t>22,75; 43,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,97; 93,92</t>
+          <t>5,99; 14,86</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,14; 98,58</t>
+          <t>1,44; 12,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,1; 91,93</t>
+          <t>8,31; 28,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,19; 97,85</t>
+          <t>2,2; 12,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80,32; 93,67</t>
+          <t>6,42; 19,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,62; 92,01</t>
+          <t>7,47; 21,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,04; 74,96</t>
+          <t>24,96; 44,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,39; 86,39</t>
+          <t>14,74; 32,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,79; 78,11</t>
+          <t>22,02; 33,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,57; 94,11</t>
+          <t>6,06; 15,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,14; 80,54</t>
+          <t>19,68; 33,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,78; 89,93</t>
+          <t>10,23; 21,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,56; 82,96</t>
+          <t>17,01; 26,32</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,51; 98,27</t>
+          <t>1,75; 15,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,0; 92,52</t>
+          <t>7,56; 31,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,62; 97,38</t>
+          <t>3,16; 17,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,18; 82,74</t>
+          <t>17,43; 33,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,69; 93,52</t>
+          <t>7,56; 22,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,44; 85,74</t>
+          <t>14,1; 33,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,39; 95,88</t>
+          <t>4,53; 21,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66,26; 80,59</t>
+          <t>20,05; 33,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,89; 94,19</t>
+          <t>5,94; 16,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72,48; 86,27</t>
+          <t>13,9; 28,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84,0; 95,03</t>
+          <t>4,98; 15,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68,83; 79,01</t>
+          <t>20,71; 31,15</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,81; 98,52</t>
+          <t>1,48; 12,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,77; 93,52</t>
+          <t>6,82; 24,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,51; 90,52</t>
+          <t>10,03; 27,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,71; 95,16</t>
+          <t>4,74; 15,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,68; 91,38</t>
+          <t>8,54; 25,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,61; 84,86</t>
+          <t>14,86; 34,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,52; 86,32</t>
+          <t>13,84; 33,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>74,68; 84,33</t>
+          <t>15,7; 26,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82,22; 93,53</t>
+          <t>6,28; 16,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,35; 86,62</t>
+          <t>13,61; 26,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,1; 86,44</t>
+          <t>13,91; 27,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,43; 87,67</t>
+          <t>12,48; 19,47</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>67,36; 93,94</t>
+          <t>6,34; 32,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,0; 90,4</t>
+          <t>9,05; 39,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,69; 100,0</t>
+          <t>0,0; 12,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,74; 90,12</t>
+          <t>9,45; 27,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,63; 89,91</t>
+          <t>10,48; 36,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,3; 81,85</t>
+          <t>19,06; 44,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,03; 88,46</t>
+          <t>12,98; 36,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>69,7; 83,12</t>
+          <t>16,83; 29,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>69,37; 88,32</t>
+          <t>11,59; 29,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,97; 83,02</t>
+          <t>17,65; 37,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77,34; 92,36</t>
+          <t>7,87; 22,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,05; 83,65</t>
+          <t>15,99; 26,98</t>
         </is>
       </c>
     </row>
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82,42; 98,03</t>
+          <t>2,01; 19,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63,16; 87,49</t>
+          <t>12,41; 36,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65,76; 88,0</t>
+          <t>12,13; 34,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69,18; 83,8</t>
+          <t>16,21; 29,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75,53; 93,78</t>
+          <t>6,86; 25,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61,19; 82,09</t>
+          <t>16,8; 39,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,05; 79,39</t>
+          <t>22,26; 47,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,84; 73,74</t>
+          <t>25,67; 39,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81,87; 94,36</t>
+          <t>6,2; 18,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66,26; 81,76</t>
+          <t>17,75; 33,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62,52; 79,63</t>
+          <t>20,37; 37,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>66,64; 77,15</t>
+          <t>23,49; 33,2</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>90,49; 98,36</t>
+          <t>1,59; 9,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>76,19; 91,78</t>
+          <t>8,16; 23,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,75; 92,3</t>
+          <t>7,53; 20,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,48; 92,89</t>
+          <t>6,99; 17,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,87; 98,47</t>
+          <t>1,55; 9,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,18; 84,58</t>
+          <t>15,36; 29,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,03; 79,61</t>
+          <t>19,82; 35,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73,46; 97,38</t>
+          <t>2,18; 26,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>92,5; 97,94</t>
+          <t>2,11; 7,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75,52; 85,91</t>
+          <t>14,07; 24,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73,39; 83,87</t>
+          <t>16,21; 26,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,41; 96,79</t>
+          <t>3,29; 19,44</t>
         </is>
       </c>
     </row>
@@ -1629,62 +1629,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>79,79; 92,66</t>
+          <t>7,7; 20,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>83,24; 95,63</t>
+          <t>3,72; 15,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,51; 94,88</t>
+          <t>4,77; 15,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87,38; 94,52</t>
+          <t>5,69; 12,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>73,1; 87,05</t>
+          <t>13,01; 25,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,0; 86,6</t>
+          <t>14,08; 26,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,16; 91,85</t>
+          <t>8,64; 20,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>77,05; 85,6</t>
+          <t>14,68; 23,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>77,69; 87,46</t>
+          <t>12,32; 22,12</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79,91; 88,89</t>
+          <t>10,94; 20,24</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83,96; 91,75</t>
+          <t>8,06; 16,23</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>82,46; 88,7</t>
+          <t>11,03; 16,75</t>
         </is>
       </c>
     </row>
@@ -1769,62 +1769,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>89,41; 94,05</t>
+          <t>5,81; 10,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>81,53; 88,33</t>
+          <t>11,66; 18,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85,61; 90,51</t>
+          <t>9,5; 14,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84,75; 88,9</t>
+          <t>11,08; 15,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83,56; 89,03</t>
+          <t>10,84; 16,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,66; 77,45</t>
+          <t>23,04; 29,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74,82; 81,4</t>
+          <t>18,75; 25,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>76,29; 89,44</t>
+          <t>9,77; 23,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86,81; 90,5</t>
+          <t>9,31; 13,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76,52; 81,09</t>
+          <t>18,96; 23,77</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80,02; 84,51</t>
+          <t>15,37; 19,56</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>80,97; 88,5</t>
+          <t>10,28; 19,11</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2073,62 +2073,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -2141,62 +2141,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37442</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52630</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31384</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55057</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68697</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64083</t>
+          <t>29092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60348</t>
+          <t>27939</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>107687</t>
+          <t>11623</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27528; 34490</t>
+          <t>905; 8428</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31300; 41301</t>
+          <t>2956; 13086</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22877; 33257</t>
+          <t>5662; 16157</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48151; 55005</t>
+          <t>1377; 8469</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31286; 39231</t>
+          <t>0; 9112</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19656; 33734</t>
+          <t>15052; 29385</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23624; 38090</t>
+          <t>11343; 26257</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49741; 58379</t>
+          <t>4659; 13654</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62647; 72578</t>
+          <t>2565; 11904</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53566; 72637</t>
+          <t>20073; 38169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50665; 68843</t>
+          <t>20084; 38806</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>101379; 112058</t>
+          <t>7143; 17731</t>
         </is>
       </c>
     </row>
@@ -2281,62 +2281,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -2349,62 +2349,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>63654</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>66301</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81810</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71112</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84292</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67136</t>
+          <t>34957</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89740</t>
+          <t>25488</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93093</t>
+          <t>35305</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>147947</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>133437</t>
+          <t>47859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171550</t>
+          <t>30973</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>164205</t>
+          <t>44902</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58752; 65706</t>
+          <t>962; 8093</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56311; 72814</t>
+          <t>6580; 22707</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76116; 85415</t>
+          <t>1924; 11274</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64827; 75602</t>
+          <t>5180; 16129</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75967; 90058</t>
+          <t>7312; 21292</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57212; 76533</t>
+          <t>25484; 45027</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78802; 99546</t>
+          <t>16986; 37897</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85756; 100293</t>
+          <t>28271; 43581</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>139136; 154831</t>
+          <t>9978; 25630</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119901; 146014</t>
+          <t>35683; 61390</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>159543; 182123</t>
+          <t>20728; 43879</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>153816; 173480</t>
+          <t>35571; 55028</t>
         </is>
       </c>
     </row>
@@ -2489,62 +2489,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -2557,62 +2557,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48006</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46475</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58389</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55115</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72428</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61778</t>
+          <t>18190</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71720</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62964</t>
+          <t>22472</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>120435</t>
+          <t>14026</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108253</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130109</t>
+          <t>13334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>118079</t>
+          <t>40847</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43048; 50060</t>
+          <t>890; 7805</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39576; 51575</t>
+          <t>4216; 17380</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53138; 61881</t>
+          <t>2007; 11141</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49369; 60803</t>
+          <t>12812; 24620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>64887; 78108</t>
+          <t>6313; 18371</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53130; 68567</t>
+          <t>11272; 26479</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63428; 76607</t>
+          <t>3620; 17015</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56608; 68849</t>
+          <t>17133; 28496</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>111457; 126644</t>
+          <t>7991; 22558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98366; 117077</t>
+          <t>18860; 38692</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120488; 136315</t>
+          <t>7142; 22468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>109391; 125565</t>
+          <t>32918; 49509</t>
         </is>
       </c>
     </row>
@@ -2697,62 +2697,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -2765,62 +2765,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>52542</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53747</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67676</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62654</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65290</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71186</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>82749</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>115197</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120587</t>
+          <t>29015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124932</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>150424</t>
+          <t>27879</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48952; 54307</t>
+          <t>818; 6893</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48516; 59881</t>
+          <t>4367; 15814</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46276; 58574</t>
+          <t>6493; 17846</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63254; 71055</t>
+          <t>3537; 11695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55495; 67911</t>
+          <t>6344; 18990</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57002; 72618</t>
+          <t>12719; 29106</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59086; 79049</t>
+          <t>12670; 31028</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>77397; 87396</t>
+          <t>16274; 26980</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>106424; 121056</t>
+          <t>8133; 21794</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>109731; 129579</t>
+          <t>20359; 39538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>114243; 135085</t>
+          <t>21736; 42911</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>143413; 156323</t>
+          <t>22258; 34711</t>
         </is>
       </c>
     </row>
@@ -2905,62 +2905,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -2973,62 +2973,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28294</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32570</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35260</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39327</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45083</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>56767</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60167</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79794</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73377</t>
+          <t>19464</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19767; 27568</t>
+          <t>1860; 9560</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19599; 28576</t>
+          <t>2861; 12531</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36481; 42080</t>
+          <t>0; 5120</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24603; 30904</t>
+          <t>3241; 9404</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26243; 37086</t>
+          <t>4321; 14915</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28069; 40806</t>
+          <t>9503; 22160</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32355; 44699</t>
+          <t>6561; 18377</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40810; 48667</t>
+          <t>9854; 17367</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>48970; 62345</t>
+          <t>8182; 21174</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51297; 67633</t>
+          <t>14379; 30295</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71625; 85536</t>
+          <t>7291; 21043</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>67818; 77660</t>
+          <t>14841; 25048</t>
         </is>
       </c>
     </row>
@@ -3113,62 +3113,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>95</t>
         </is>
       </c>
     </row>
@@ -3181,62 +3181,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>43509</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>40053</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46651</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>60743</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51104</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45283</t>
+          <t>22105</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>43885</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>104252</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>91157</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83709</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90536</t>
+          <t>34983</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38901; 46265</t>
+          <t>951; 9235</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32688; 45282</t>
+          <t>6423; 18977</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31859; 42632</t>
+          <t>5877; 16532</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41687; 50501</t>
+          <t>9766; 17832</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>53102; 65938</t>
+          <t>4822; 17858</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42966; 57634</t>
+          <t>11792; 27413</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36422; 53500</t>
+          <t>15001; 32096</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39048; 48123</t>
+          <t>16750; 25667</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96200; 110875</t>
+          <t>7288; 21614</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80815; 99718</t>
+          <t>21651; 40396</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72415; 92239</t>
+          <t>23597; 43176</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>83646; 96844</t>
+          <t>29479; 41669</t>
         </is>
       </c>
     </row>
@@ -3321,62 +3321,62 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>41</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -3389,62 +3389,62 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>101563</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>95755</t>
+          <t>16508</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97487</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108027</t>
+          <t>14496</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>112271</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>107873</t>
+          <t>39752</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>305247</t>
+          <t>32259</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>213834</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>206766</t>
+          <t>47460</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205359</t>
+          <t>54451</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>413274</t>
+          <t>46755</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>95858; 104196</t>
+          <t>1686; 9617</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>85537; 103034</t>
+          <t>9166; 26926</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89468; 103542</t>
+          <t>8447; 23034</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>101060; 113810</t>
+          <t>8566; 21518</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>106429; 115332</t>
+          <t>1813; 11121</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>99631; 120073</t>
+          <t>21805; 41969</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94528; 117522</t>
+          <t>29266; 51759</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>247924; 328649</t>
+          <t>7358; 89449</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>206327; 218455</t>
+          <t>4704; 16198</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>191994; 218410</t>
+          <t>35766; 61714</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>190686; 217899</t>
+          <t>42124; 68887</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>369930; 445256</t>
+          <t>15128; 89445</t>
         </is>
       </c>
     </row>
@@ -3529,62 +3529,62 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>38</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>81</t>
         </is>
       </c>
     </row>
@@ -3597,62 +3597,62 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>97227</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>109872</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>121939</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>133704</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>123957</t>
+          <t>29268</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>132305</t>
+          <t>32112</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>152670</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>151683</t>
+          <t>33936</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>221184</t>
+          <t>43934</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>242177</t>
+          <t>42992</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>274609</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>285387</t>
+          <t>46707</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>89279; 103681</t>
+          <t>8612; 22601</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>100510; 115473</t>
+          <t>4487; 18895</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>113387; 127296</t>
+          <t>6394; 20121</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>127986; 138452</t>
+          <t>8330; 19008</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>112012; 133376</t>
+          <t>19928; 39823</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>121665; 142393</t>
+          <t>23156; 43291</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>141327; 161929</t>
+          <t>15239; 36198</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>143028; 158890</t>
+          <t>27255; 43754</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>205960; 231861</t>
+          <t>32666; 58652</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>227868; 253473</t>
+          <t>31204; 57704</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>260668; 284844</t>
+          <t>25013; 50383</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>273839; 294576</t>
+          <t>36629; 55616</t>
         </is>
       </c>
     </row>
@@ -3737,62 +3737,62 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>386</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>126</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>248</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>526</t>
         </is>
       </c>
     </row>
@@ -3805,62 +3805,62 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>462565</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>476102</t>
+          <t>83535</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>521230</t>
+          <t>70098</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>563210</t>
+          <t>85110</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>585747</t>
+          <t>91095</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>550525</t>
+          <t>192450</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>609182</t>
+          <t>168749</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>839761</t>
+          <t>188049</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1048312</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1026627</t>
+          <t>275985</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1130412</t>
+          <t>238847</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1402970</t>
+          <t>273160</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>449238; 472568</t>
+          <t>29182; 52301</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>456251; 494339</t>
+          <t>65275; 101241</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>506213; 535239</t>
+          <t>56165; 86052</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>549445; 576379</t>
+          <t>71839; 99136</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>565581; 602613</t>
+          <t>73382; 109071</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>524999; 575445</t>
+          <t>171211; 219312</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>582046; 633231</t>
+          <t>145837; 198271</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>784166; 919250</t>
+          <t>100373; 241687</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1023807; 1067262</t>
+          <t>109799; 153994</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>996815; 1056237</t>
+          <t>246971; 309586</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1095662; 1157194</t>
+          <t>210422; 267800</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1357089; 1483384</t>
+          <t>172260; 320343</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/BARTHEL_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/BARTHEL_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 23,82</t>
+          <t>2,5; 22,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 29,55</t>
+          <t>6,68; 29,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 41,54</t>
+          <t>14,5; 39,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,15</t>
+          <t>1,45; 13,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,23</t>
+          <t>0,0; 18,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,78; 60,1</t>
+          <t>32,39; 60,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,97; 53,16</t>
+          <t>22,35; 50,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,35; 21,53</t>
+          <t>7,72; 19,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 15,95</t>
+          <t>3,43; 15,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,54; 40,96</t>
+          <t>21,8; 42,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,75; 43,95</t>
+          <t>22,39; 42,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 14,86</t>
+          <t>5,61; 13,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,14</t>
+          <t>1,44; 12,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 28,67</t>
+          <t>7,21; 27,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,91</t>
+          <t>2,59; 13,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 19,98</t>
+          <t>6,3; 19,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 21,75</t>
+          <t>7,71; 22,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,96; 44,1</t>
+          <t>25,43; 44,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,74; 32,89</t>
+          <t>13,98; 31,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,02; 33,94</t>
+          <t>22,61; 34,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 15,58</t>
+          <t>6,07; 15,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,68; 33,86</t>
+          <t>20,14; 33,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,23; 21,67</t>
+          <t>10,43; 21,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,01; 26,32</t>
+          <t>17,24; 26,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 15,32</t>
+          <t>1,75; 15,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 31,18</t>
+          <t>7,62; 30,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 17,53</t>
+          <t>3,57; 15,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,43; 33,5</t>
+          <t>17,81; 32,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 22,0</t>
+          <t>6,67; 22,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,1; 33,11</t>
+          <t>13,93; 33,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 21,3</t>
+          <t>3,26; 20,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,05; 33,35</t>
+          <t>20,57; 34,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 16,78</t>
+          <t>6,04; 16,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 28,51</t>
+          <t>14,25; 28,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 15,66</t>
+          <t>5,28; 16,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,71; 31,15</t>
+          <t>21,34; 31,27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 12,5</t>
+          <t>1,49; 12,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 24,7</t>
+          <t>6,48; 24,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 27,58</t>
+          <t>9,6; 27,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 15,66</t>
+          <t>4,16; 14,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,54; 25,55</t>
+          <t>8,46; 25,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 34,01</t>
+          <t>16,08; 33,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,84; 33,88</t>
+          <t>13,29; 33,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,7; 26,03</t>
+          <t>15,3; 25,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 16,84</t>
+          <t>6,26; 17,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,61; 26,43</t>
+          <t>13,52; 26,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,91; 27,46</t>
+          <t>13,96; 27,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 19,47</t>
+          <t>11,7; 18,65</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 32,57</t>
+          <t>8,11; 32,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 39,64</t>
+          <t>7,54; 41,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,17</t>
+          <t>0,0; 13,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 27,42</t>
+          <t>9,54; 26,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 36,16</t>
+          <t>8,76; 36,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,06; 44,45</t>
+          <t>16,43; 41,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,98; 36,37</t>
+          <t>11,19; 35,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,83; 29,66</t>
+          <t>17,25; 31,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 29,99</t>
+          <t>11,2; 30,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,65; 37,19</t>
+          <t>17,13; 37,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,87; 22,72</t>
+          <t>7,57; 21,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 26,98</t>
+          <t>15,72; 26,74</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 19,57</t>
+          <t>1,99; 17,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,41; 36,67</t>
+          <t>12,37; 35,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,13; 34,13</t>
+          <t>10,62; 32,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,21; 29,59</t>
+          <t>16,12; 29,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,86; 25,4</t>
+          <t>6,49; 24,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,8; 39,04</t>
+          <t>17,94; 39,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,26; 47,63</t>
+          <t>20,53; 46,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,67; 39,33</t>
+          <t>26,09; 40,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 18,39</t>
+          <t>6,34; 18,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,75; 33,12</t>
+          <t>17,84; 33,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,37; 37,27</t>
+          <t>19,95; 37,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,49; 33,2</t>
+          <t>23,4; 33,4</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,08</t>
+          <t>1,59; 9,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,16; 23,98</t>
+          <t>8,97; 24,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,53; 20,53</t>
+          <t>8,05; 20,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 17,56</t>
+          <t>7,12; 17,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 9,5</t>
+          <t>1,65; 9,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,36; 29,56</t>
+          <t>15,31; 30,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,82; 35,06</t>
+          <t>19,17; 35,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 26,5</t>
+          <t>19,0; 30,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,26</t>
+          <t>1,98; 7,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,07; 24,28</t>
+          <t>13,99; 24,69</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,21; 26,51</t>
+          <t>15,76; 26,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 19,44</t>
+          <t>14,43; 21,8</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,7; 20,2</t>
+          <t>7,7; 20,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,72; 15,65</t>
+          <t>4,56; 16,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,77; 15,0</t>
+          <t>5,11; 15,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,69; 12,98</t>
+          <t>5,83; 13,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,01; 25,99</t>
+          <t>13,25; 26,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,08; 26,33</t>
+          <t>14,03; 27,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,64; 20,53</t>
+          <t>8,72; 20,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,68; 23,57</t>
+          <t>14,75; 23,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,32; 22,12</t>
+          <t>12,3; 21,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,94; 20,24</t>
+          <t>11,38; 20,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,06; 16,23</t>
+          <t>8,26; 16,32</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,03; 16,75</t>
+          <t>11,82; 17,81</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,41</t>
+          <t>6,2; 10,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,66; 18,09</t>
+          <t>11,98; 18,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1852,47 +1852,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,08; 15,29</t>
+          <t>10,62; 14,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,84; 16,11</t>
+          <t>11,15; 16,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,04; 29,52</t>
+          <t>22,45; 28,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,75; 25,49</t>
+          <t>18,76; 25,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,77; 23,51</t>
+          <t>20,85; 25,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,31; 13,06</t>
+          <t>9,36; 12,99</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18,96; 23,77</t>
+          <t>18,97; 23,56</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,37; 19,56</t>
+          <t>15,45; 19,73</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,28; 19,11</t>
+          <t>16,9; 20,01</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11690</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>905; 8428</t>
+          <t>885; 8133</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2956; 13086</t>
+          <t>2958; 13261</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5662; 16157</t>
+          <t>5639; 15399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1377; 8469</t>
+          <t>881; 8078</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 9112</t>
+          <t>0; 7176</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15052; 29385</t>
+          <t>15839; 29537</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11343; 26257</t>
+          <t>11041; 25060</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4659; 13654</t>
+          <t>5037; 12753</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2565; 11904</t>
+          <t>2562; 11856</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20073; 38169</t>
+          <t>20314; 39148</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20084; 38806</t>
+          <t>19769; 37634</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7143; 17731</t>
+          <t>7076; 17365</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35305</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44902</t>
+          <t>48152</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>962; 8093</t>
+          <t>962; 8038</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6580; 22707</t>
+          <t>5712; 21760</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1924; 11274</t>
+          <t>2262; 11724</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5180; 16129</t>
+          <t>5568; 16816</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7312; 21292</t>
+          <t>7547; 22105</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25484; 45027</t>
+          <t>25965; 45107</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16986; 37897</t>
+          <t>16108; 36190</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28271; 43581</t>
+          <t>30464; 46590</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9978; 25630</t>
+          <t>9990; 25362</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35683; 61390</t>
+          <t>36504; 61358</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20728; 43879</t>
+          <t>21127; 43134</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35571; 55028</t>
+          <t>38462; 58910</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40847</t>
+          <t>40593</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>890; 7805</t>
+          <t>893; 8042</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4216; 17380</t>
+          <t>4247; 17235</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2007; 11141</t>
+          <t>2270; 10090</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12812; 24620</t>
+          <t>12874; 23170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6313; 18371</t>
+          <t>5570; 18880</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11272; 26479</t>
+          <t>11143; 26625</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3620; 17015</t>
+          <t>2608; 16491</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17133; 28496</t>
+          <t>17293; 28906</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7991; 22558</t>
+          <t>8125; 22323</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18860; 38692</t>
+          <t>19337; 38578</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7142; 22468</t>
+          <t>7579; 23638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32918; 49509</t>
+          <t>33366; 48891</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>21869</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27879</t>
+          <t>29010</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>818; 6893</t>
+          <t>823; 6966</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4367; 15814</t>
+          <t>4150; 15409</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6493; 17846</t>
+          <t>6210; 18048</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3537; 11695</t>
+          <t>3461; 11756</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6344; 18990</t>
+          <t>6290; 19315</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12719; 29106</t>
+          <t>13763; 29052</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12670; 31028</t>
+          <t>12172; 30417</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16274; 26980</t>
+          <t>16908; 27726</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8133; 21794</t>
+          <t>8097; 22324</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20359; 39538</t>
+          <t>20225; 39617</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21736; 42911</t>
+          <t>21816; 43032</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22258; 34711</t>
+          <t>22657; 36126</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>20256</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1860; 9560</t>
+          <t>2380; 9487</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2861; 12531</t>
+          <t>2385; 13044</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5120</t>
+          <t>0; 5744</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3241; 9404</t>
+          <t>3435; 9610</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4321; 14915</t>
+          <t>3614; 15006</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9503; 22160</t>
+          <t>8190; 20839</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6561; 18377</t>
+          <t>5653; 17854</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9854; 17367</t>
+          <t>10489; 19046</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8182; 21174</t>
+          <t>7905; 21389</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14379; 30295</t>
+          <t>13957; 30683</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7291; 21043</t>
+          <t>7013; 20207</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14841; 25048</t>
+          <t>15217; 25886</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>22158</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34983</t>
+          <t>35801</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>951; 9235</t>
+          <t>938; 8450</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6423; 18977</t>
+          <t>6400; 18125</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5877; 16532</t>
+          <t>5143; 15602</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9766; 17832</t>
+          <t>9707; 18023</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4822; 17858</t>
+          <t>4563; 17397</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11792; 27413</t>
+          <t>12596; 27391</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15001; 32096</t>
+          <t>13837; 31067</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16750; 25667</t>
+          <t>17562; 27139</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7288; 21614</t>
+          <t>7447; 21845</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21651; 40396</t>
+          <t>21760; 40421</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23597; 43176</t>
+          <t>23115; 43140</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29479; 41669</t>
+          <t>29841; 42598</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14496</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>32259</t>
+          <t>39505</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>46755</t>
+          <t>56700</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1686; 9617</t>
+          <t>1683; 9691</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9166; 26926</t>
+          <t>10069; 27434</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8447; 23034</t>
+          <t>9027; 22660</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8566; 21518</t>
+          <t>10711; 26320</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1813; 11121</t>
+          <t>1931; 10988</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21805; 41969</t>
+          <t>21734; 42998</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29266; 51759</t>
+          <t>28306; 52009</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7358; 89449</t>
+          <t>30945; 48904</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4704; 16198</t>
+          <t>4426; 15798</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35766; 61714</t>
+          <t>35574; 62769</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42124; 68887</t>
+          <t>40933; 67588</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15128; 89445</t>
+          <t>45182; 68279</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>33936</t>
+          <t>39877</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>46707</t>
+          <t>54746</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8612; 22601</t>
+          <t>8618; 23160</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4487; 18895</t>
+          <t>5504; 20440</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6394; 20121</t>
+          <t>6859; 21105</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8330; 19008</t>
+          <t>9505; 21651</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19928; 39823</t>
+          <t>20303; 41196</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23156; 43291</t>
+          <t>23074; 44509</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15239; 36198</t>
+          <t>15367; 35620</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27255; 43754</t>
+          <t>31209; 48810</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>32666; 58652</t>
+          <t>32616; 58065</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31204; 57704</t>
+          <t>32455; 57648</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25013; 50383</t>
+          <t>25636; 50664</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>36629; 55616</t>
+          <t>44284; 66715</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>85110</t>
+          <t>90364</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>188049</t>
+          <t>206583</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>273160</t>
+          <t>296947</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>29182; 52301</t>
+          <t>31162; 53936</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>65275; 101241</t>
+          <t>67035; 102984</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56165; 86052</t>
+          <t>56185; 86038</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>71839; 99136</t>
+          <t>75881; 105557</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>73382; 109071</t>
+          <t>75498; 111199</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>171211; 219312</t>
+          <t>166780; 215353</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>145837; 198271</t>
+          <t>145972; 195591</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>100373; 241687</t>
+          <t>187084; 226763</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>109799; 153994</t>
+          <t>110431; 153159</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>246971; 309586</t>
+          <t>247130; 306910</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>210422; 267800</t>
+          <t>211551; 270154</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>172260; 320343</t>
+          <t>272374; 322447</t>
         </is>
       </c>
     </row>
